--- a/AAII_Financials/Quarterly/SSREY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSREY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="92">
   <si>
     <t>SSREY</t>
   </si>
@@ -656,68 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +760,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +804,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +848,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +868,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +910,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +954,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +998,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1042,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1059,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1101,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1145,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1165,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1207,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1251,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1295,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1339,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1383,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1427,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1471,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1515,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1559,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1603,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1647,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1691,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1735,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1779,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1823,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1867,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +1936,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,131 +1954,141 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3930000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2743000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3669000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4133000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3292000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3392000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4151000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3656000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4662000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5288000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4151000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4058000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3656000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3300000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3131000</v>
       </c>
-      <c r="E42" s="3">
-        <v>1297000</v>
-      </c>
       <c r="F42" s="3">
+        <v>1950000</v>
+      </c>
+      <c r="G42" s="3">
         <v>3307000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>11156000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8963000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9788000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9161000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8126000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8963000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7378000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9788000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4283000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4107000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4057000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3540000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3074000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19607000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22525000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18501000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20345000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>22525000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>18501000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2033,158 +2128,170 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7825000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7675000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7915000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8232000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6704000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9664000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9659000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9108000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10206000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>41986000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9659000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43411000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9108000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19338000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17656000</v>
       </c>
-      <c r="E46" s="3">
-        <v>16938000</v>
-      </c>
       <c r="F46" s="3">
+        <v>17591000</v>
+      </c>
+      <c r="G46" s="3">
         <v>19212000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13070000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45010000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45463000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41474000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44989000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55400000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45463000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54847000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41474000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>94500000</v>
+      </c>
+      <c r="E47" s="3">
         <v>97893000</v>
       </c>
-      <c r="E47" s="3">
-        <v>100412000</v>
-      </c>
       <c r="F47" s="3">
+        <v>99759000</v>
+      </c>
+      <c r="G47" s="3">
         <v>91199000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>94807000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>69670000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>70772000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>69455000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70824000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93645000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>70772000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>97603000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>69455000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>224000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3">
         <v>234000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
         <v>406000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>396000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2194,52 +2301,58 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4009000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4020000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4038000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4050000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4083000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12853000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13043000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12778000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12872000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12752000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13043000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13138000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12778000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2392,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2436,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5277000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5371000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5200000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4454000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7140000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39204000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>36660000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33946000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35016000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14419000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36660000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14299000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33946000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2524,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>132845000</v>
+      </c>
+      <c r="E54" s="3">
         <v>134007000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>135341000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>127229000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>127519000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>179576000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>179030000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>170676000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>175244000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>176216000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>179030000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>179887000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>170676000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2588,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2606,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3819000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4039000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3737000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3920000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3862000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>98706000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>96414000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94176000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91257000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>112614000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>96414000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>115123000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94176000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E58" s="3">
         <v>451000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1307000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1127000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1031000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3778000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1459000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2117000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2132000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1266000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1459000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2117000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1881000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1930000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3223000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2233000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2425000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16687000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20976000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15997000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20187000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>20976000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>15997000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6067000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6420000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8267000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7280000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7318000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119171000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>118849000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>112290000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>113576000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>113880000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>118849000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>115923000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>112290000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9076000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8772000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8475000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7359000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7305000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8908000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10650000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10622000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10633000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9737000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10650000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10360000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10622000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>89864000</v>
+      </c>
+      <c r="E62" s="3">
         <v>90276000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>91716000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>86937000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>87314000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28912000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30475000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29127000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30077000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39690000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30475000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39250000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29127000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +2912,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +2956,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3000,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107888000</v>
+      </c>
+      <c r="E66" s="3">
         <v>108268000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>111270000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>103989000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>105109000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>163205000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>166176000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>157867000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>160325000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163307000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>166176000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>165533000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>157867000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3064,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3106,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3150,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3194,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3238,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28225000</v>
+      </c>
+      <c r="E72" s="3">
         <v>27752000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26021000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26166000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24731000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28548000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26781000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27279000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26964000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>26781000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>27279000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3326,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3370,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3414,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24900000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25558000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23925000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23106000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22275000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16146000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12680000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12699000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14807000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12698000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12680000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14225000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12699000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3502,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3595,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,8 +3615,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3441,14 +3639,14 @@
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="3">
-        <v>17500</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>17500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
+      <c r="L83" s="3">
+        <v>17500</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
@@ -3459,8 +3657,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3701,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3745,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3789,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +3833,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,8 +3877,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3705,8 +3921,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,8 +3941,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3763,8 +3983,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4027,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,8 +4071,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3886,8 +4115,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,8 +4135,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3944,8 +4177,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4221,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4265,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,8 +4309,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4108,8 +4353,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4131,14 +4379,14 @@
       <c r="I101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J101" s="3">
-        <v>171000</v>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>171000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
+      <c r="L101" s="3">
+        <v>171000</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
@@ -4149,8 +4397,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4178,16 +4429,19 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
